--- a/光伏配储项目/电价数据/2026/翌川站.xlsx
+++ b/光伏配储项目/电价数据/2026/翌川站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50979</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.68916</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56263</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.49249</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.44003</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.43433</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43795</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43935</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42328</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41435</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44434</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26079</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.19219</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.24438</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.06615</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.05502000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.03775</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.03738</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03796</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.03262</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.01989</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08524</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.02282</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.01884</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00156</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14458</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21253</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23517</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18317</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.08876000000000001</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.03544</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01044</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.09591</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11396</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.15678</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.20967</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.14131</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.11973</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.10328</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.16745</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.18432</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.42123</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.51801</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7212799999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.60845</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.48514</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.45596</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.37232</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5518099999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.52364</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.15777</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.47912</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.48458</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.5807899999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.53818</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47869</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42012</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.60684</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.39877</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7398400000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.94656</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7996599999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5372400000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52408</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5066700000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5031600000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50254</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47444</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42305</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.51698</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6299199999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7223999999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.4338</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.07481</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.25045</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.25902</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26356</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.21796</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.57599</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.01791</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.26777</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.25375</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.28619</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.22459</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.55206</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27059</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.21258</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.15185</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.21579</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.21809</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23028</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.24951</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.28948</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.20959</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.19783</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68589</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7948500000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.78703</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.18232</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8027300000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.74854</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.27473</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43539</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5903099999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43884</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43307</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40675</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33289</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5157999999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.46788</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43258</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47404</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44833</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44271</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.27102</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28277</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27864</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.27228</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.2466</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28049</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.22682</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27894</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.05195</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.19645</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.12308</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.17221</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24104</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.25091</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.24978</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.20038</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.15328</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.26258</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.44849</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.48045</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.28007</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.27622</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.24298</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.25513</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.27882</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34341</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.28601</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47054</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28089</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26304</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.20053</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12016</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11283</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08406</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.18955</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06358</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.25403</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.20139</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.03565</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.03205</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.25435</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.01397</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.02744</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.05361999999999999</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.09051000000000001</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.24972</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.2221</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.18027</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.22966</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16069</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.23399</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.25069</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25986</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.27858</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.28676</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41978</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48388</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.40796</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.39395</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.27683</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29105</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28277</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.28624</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04017</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04532</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.03994</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04296</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04613</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04451</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04654</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04213</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04654</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04618</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04466</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04361</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04601</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04918</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04507</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.0458</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04725</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04714</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04506</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04697</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22031</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04727000000000001</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05118</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05338</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00256</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14651</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03692</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09845000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37435</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35139</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6636299999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10242</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04247</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04627000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04576</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04453</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04255</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03197</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04134</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10656</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00046</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03765</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04706</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04206</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04216</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04205</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04436</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04427</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04425</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04201</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04145</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04126</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03979</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04428</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04182</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04047</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04373</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04683</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04671</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20151</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14409</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2705</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33703</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32089</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28276</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27273</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27271</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28258</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17365</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17247</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14896</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16069</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15999</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23844</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21541</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22796</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27111</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.26945</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.26636</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.40341</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.39349</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29878</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15735</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79111</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6218899999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78083</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.91995</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49425</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92338</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8930900000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31166</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.91606</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63628</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.2151</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88251</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.56637</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.35965</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.05264</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.55976</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.81567</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7977799999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.79722</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87982</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88683</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.51634</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42968</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.47642</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.23678</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8796799999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5515399999999999</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.65137</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5456799999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50618</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42773</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44235</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45134</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45306</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42153</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41024</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58873</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59663</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60158</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6554500000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45175</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55453</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44643</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8621</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.66334</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.82913</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.81216</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8469800000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43258</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27125</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45288</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35338</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.98868</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.48791</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.45306</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.54784</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.61617</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.4611</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.41434</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16457</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26084</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20057</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.25788</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27503</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.26855</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27543</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43178</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27608</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44773</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59782</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88967</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35083</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14031</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7075199999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80033</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65227</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5877899999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5010899999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43414</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42845</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.56549</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.06727</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.48933</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.0398</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.6757300000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.21966</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.55165</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26582</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26681</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26578</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.43961</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.58728</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46453</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7141799999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46585</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4387200000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42466</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32573</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42475</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.25875</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14502</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14735</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15421</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1444</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14086</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14418</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14266</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25747</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14473</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26682</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26719</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14219</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.03511</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11418</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11328</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14547</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14153</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14672</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45085</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44088</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44109</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44048</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44542</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44488</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35011</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.55213</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46978</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42482</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.26722</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.26316</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.23716</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23269</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.18164</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.27388</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.23791</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21508</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.23967</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.27198</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.26095</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.28864</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.26962</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.21514</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.27365</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.27164</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.25634</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.4216</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24402</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41808</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.44828</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36055</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28035</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.40615</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.27311</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26491</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.04014</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.24886</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24993</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.19518</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07004000000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.17722</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24395</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.26608</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.24794</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.28424</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.26728</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.40936</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.47005</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.73129</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.44856</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40523</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30115</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27763</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40448</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34923</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28059</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.60488</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42333</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38626</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.61287</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7757000000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.46188</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.41909</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44886</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34504</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26049</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13336</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19449</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24409</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27827</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.02279</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.02341</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28386</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23057</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28696</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24037</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14371</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.20856</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.21632</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.28545</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41426</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.60998</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.58002</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.57464</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.5909099999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.45793</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.67125</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43507</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.44206</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39505</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.46291</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42109</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36023</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.47454</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.44474</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.44563</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.43467</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41381</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39658</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40771</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40564</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41275</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40784</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40579</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38655</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41145</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44027</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.43937</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.53461</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.48295</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44038</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42689</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.28575</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.23708</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.12381</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.00548</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.01657</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.67557</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.26215</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.07945999999999999</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.25179</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.0124</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.40506</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.46833</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.41911</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.48862</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.48977</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.54338</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.6372100000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.6329400000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.6120399999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.50769</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.50254</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.75487</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.6990499999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.57133</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.61394</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.42604</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46665</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.46439</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.45898</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50817</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44695</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.43841</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41215</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39759</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44641</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40302</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.26202</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03464</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40886</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45524</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46593</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.03416</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18445</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40824</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39745</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.364</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.4436</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.23957</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23265</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23412</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.23423</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24771</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13044</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.23065</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28789</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.00991</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.15975</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25615</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.004889999999999999</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14504</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15322</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.02938</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.04090999999999999</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21516</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22528</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.14819</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21009</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26472</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2835</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35225</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.2254</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21549</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15019</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.17869</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04468</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01584</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00185</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04356</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.05554</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03428</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04183</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.03528</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0488</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.03421</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.16825</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21369</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24342</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24469</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24516</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.24958</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26239</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27105</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26741</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25603</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27563</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.27887</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.2666</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26539</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23255</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.17537</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05173</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.00294</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.05997</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.24496</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22207</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22172</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.13926</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.25937</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24174</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.21945</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20393</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.18687</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21091</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22426</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.16697</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.18672</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22159</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.21722</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2427</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.22991</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.25965</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22318</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.26685</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24493</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24774</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.05981</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.48491</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.49273</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.22029</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02836</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.19999</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09024</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.03893</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.05144</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.01139</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20706</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.02826</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.00605</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02308</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.12859</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03935</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.03697</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.07806999999999999</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02234</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.00869</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02383</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.04401</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23134</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.27845</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.24857</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.16142</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32531</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.11064</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.22775</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23409</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.2392</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.11236</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.22955</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.28986</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.11024</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25303</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26969</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.16671</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14834</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.07287</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3312</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.26217</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.2601</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.49514</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50292</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.23505</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.28534</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.25893</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.25427</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.25475</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.27757</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25671</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.23086</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.26482</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.26591</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46329</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.47615</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45754</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.47342</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.04933</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.43367</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.39594</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47188</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.43172</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.41696</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42595</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.74648</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45931</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40173</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36898</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46546</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.28399</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.29447</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.2728</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.18091</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.15131</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.22853</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.25097</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.17372</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.28656</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.25065</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.25912</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.42996</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.40377</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45842</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5561499999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5522400000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45772</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5465800000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.45757</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.48963</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53043</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5210399999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.72742</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.76908</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54437</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.54652</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44332</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37568</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27324</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.27921</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27265</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.25764</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.25701</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27333</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20719</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23159</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13059</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.02464</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.13627</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.008449999999999999</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.09448999999999999</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01445</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.04136</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02519</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23342</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.04182</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.01961</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03289</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02347</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.00925</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01166</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.11895</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06177000000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.12832</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.14072</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.17191</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.24118</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18792</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.15589</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.22175</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41351</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37839</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8009400000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.27488</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.24267</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.21309</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.21273</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.21684</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.23866</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.08087000000000001</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.00174</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03519</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.1105</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.02459</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00328</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01306</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04507</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01361</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01355</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.02178</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.17196</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.02711</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.15845</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13277</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.14761</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.17271</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.11122</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.20112</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.18988</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.2377</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.22144</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.27096</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5206000000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42708</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38814</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38691</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5184</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41959</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25385</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.2173</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.19818</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.12748</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.17544</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.20253</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.19571</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.10266</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.12617</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.05183</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.08422</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03593</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03697</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03678</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03532</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04621</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05364</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06778000000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06219</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.08461</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.13963</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.17819</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.10195</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.20561</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.18129</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.10584</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04805</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.23499</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.11965</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.10504</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2094</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.1565</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.17494</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.20304</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.17281</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21025</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23349</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23444</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.2499</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40793</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41363</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49258</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41331</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.43094</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40977</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38403</v>
       </c>
     </row>
   </sheetData>
